--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -384,7 +384,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -384,7 +384,7 @@
     </row>
     <row r="2" spans="1:1">
       <c r="A2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -1,48 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rerun At The End" sheetId="1" r:id="rId1"/>
+    <sheet name="Rerun Count" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Rerun Count</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,21 +420,417 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rerun Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_DaAlerts_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Signature_01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Void_01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Promo_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Logout_Success_01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Login_Invalid_01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_UPI_01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_BQR_01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Filters_01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_ChargeSlip_01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Disabled_01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Enabled_01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_SendReceipt_01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_PrintReceipt_01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_02</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_to_Hindi_03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_to_English_04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Lang_selection_05</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Upfront_Mobile_Number_01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>test_success</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>test_success_2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_001</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_002</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Pending_HDFC_05</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Refund_HDFC_03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Expire_HDFC_06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Failed_Via_SA_CheckStatus_HDFC</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_003</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_005</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_006</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_007</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_009</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_008</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_004</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>test_API_SA_PreFetch_01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Axis_02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Hdfc_03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
         <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -1,48 +1,37 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rerun At The End" sheetId="1" r:id="rId1"/>
+    <sheet name="Rerun Count" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Rerun Count</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -57,35 +46,93 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,21 +420,417 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
-        <v>1</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rerun Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_DaAlerts_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Signature_01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Void_01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Promo_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Logout_Success_01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Login_Invalid_01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_UPI_01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_BQR_01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Filters_01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_ChargeSlip_01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Disabled_01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Enabled_01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_SendReceipt_01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_PrintReceipt_01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_02</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_to_Hindi_03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_to_English_04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Lang_selection_05</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Upfront_Mobile_Number_01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>test_success</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>test_success_2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_001</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_002</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Pending_HDFC_05</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Refund_HDFC_03</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Expire_HDFC_06</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_MPOS_PM_UPI_Failed_Via_SA_CheckStatus_HDFC</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_003</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_005</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_006</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_007</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_009</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_008</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_004</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>test_API_SA_PreFetch_01</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Axis_02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Hdfc_03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -1,48 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rerun At The End" sheetId="1" r:id="rId1"/>
+    <sheet name="Rerun At The End" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Rerun Count</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -76,16 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,18 +433,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Rerun Count</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
-        <v>2</v>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -1,41 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Rerun At The End" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Rerun At The End" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+  <si>
+    <t>Rerun Count</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -69,83 +76,16 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -433,24 +373,18 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:A2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Rerun Count</t>
-        </is>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="n">
-        <v>0</v>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -1,48 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Rerun At The End" sheetId="1" r:id="rId1"/>
+    <sheet name="Rerun Count" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
+  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Rerun Count</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -76,16 +69,83 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -373,17 +433,613 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Rerun Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_DaAlerts_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Signature_01</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Void_01</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Promo_Displayed_01</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Logout_Success_01</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Login_Invalid_01</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_UPI_01</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_CheckStatus_BQR_01</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_Filters_01</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_ChargeSlip_01</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Disabled_01</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_AutoLogin_Enabled_01</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_SendReceipt_01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_TxnHistory_PrintReceipt_01</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_01</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_02</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_English_to_Hindi_03</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Hindi_to_English_04</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Multilanguage_Lang_selection_05</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>test_UI_SA_Upfront_Mobile_Number_01</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>test_success</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>test_success_2</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_001</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_002</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_101_003</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_102_007</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_102_008</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_102_009</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_102_010</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>test_sa_100_102_011</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_004</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_005</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_006</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_007</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_008</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_009</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_010</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_011</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_012</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_013</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>test_com_100_101_014</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_001</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_002</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_003</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_004</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_005</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_006</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_019</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_020</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_021</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_022</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_102_025</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_103_001</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_103_002</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>test_common_100_103_003</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>test_API_SA_PreFetch_01</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Ezetap_01</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Axis_02</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>test_GUI_APP_Branding_Hdfc_03</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
         <v>1</v>
       </c>
     </row>

--- a/TestCases/RerunCount.xlsx
+++ b/TestCases/RerunCount.xlsx
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="26">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="44">
@@ -930,7 +930,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="50">
@@ -980,7 +980,7 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -990,7 +990,7 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="57">
